--- a/CDF_Template_Base.xlsx
+++ b/CDF_Template_Base.xlsx
@@ -4076,61 +4076,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>49100</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>49100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1537203</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>16172</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="49100" y="49100"/>
-          <a:ext cx="1875735" cy="697191"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>

--- a/CDF_Template_Base.xlsx
+++ b/CDF_Template_Base.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/37e8bf313699c053/Samaritan's Purse/apprentice/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larrington/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{CEA1AC9F-2DAA-4912-BA49-7BEB6AF08465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B14C688-4E86-0347-BA13-D0E0A71082D7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E1A796B-5D25-1443-AB5D-6DFB01C742DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="13600" windowHeight="15260" xr2:uid="{DFCFC3C2-3019-4FCB-9E60-88B081D83644}"/>
+    <workbookView xWindow="1200" yWindow="500" windowWidth="13600" windowHeight="15260" xr2:uid="{DFCFC3C2-3019-4FCB-9E60-88B081D83644}"/>
   </bookViews>
   <sheets>
     <sheet name="Cash Disbursement" sheetId="1" r:id="rId1"/>
@@ -554,7 +554,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="72">
   <si>
     <t xml:space="preserve">  CASH DISBURSEMENT FORM</t>
   </si>
@@ -1726,7 +1726,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="205">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1800,10 +1800,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="43" fontId="4" fillId="2" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1858,18 +1854,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1952,14 +1940,561 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="2" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="2" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="37" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="20" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="49" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="51" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -1976,397 +2511,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="56" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="37" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="20" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="49" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="51" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="2" borderId="54" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="2" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="43" fontId="5" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2375,159 +2519,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2846,7 +2842,7 @@
   <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="31" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" style="26" customWidth="1"/>
+    <col min="1" max="1" width="3.83203125" style="25" customWidth="1"/>
     <col min="2" max="2" width="28.1640625" style="4" customWidth="1"/>
     <col min="3" max="3" width="29.5" style="4" customWidth="1"/>
     <col min="4" max="4" width="17.33203125" style="4" customWidth="1"/>
@@ -2854,10 +2850,10 @@
     <col min="6" max="6" width="13.5" style="4" customWidth="1"/>
     <col min="7" max="7" width="7.5" style="4" customWidth="1"/>
     <col min="8" max="8" width="9.6640625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="6.83203125" style="27" customWidth="1"/>
-    <col min="10" max="10" width="7.5" style="28" customWidth="1"/>
-    <col min="11" max="11" width="3.5" style="27" customWidth="1"/>
-    <col min="12" max="12" width="22.5" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.83203125" style="26" customWidth="1"/>
+    <col min="10" max="10" width="7.5" style="27" customWidth="1"/>
+    <col min="11" max="11" width="3.5" style="26" customWidth="1"/>
+    <col min="12" max="12" width="22.5" style="27" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.1640625" style="4"/>
     <col min="14" max="14" width="12.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.1640625" style="4"/>
@@ -2868,123 +2864,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="2" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="196" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="174" t="s">
+      <c r="B1" s="197"/>
+      <c r="C1" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="174"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="174"/>
-      <c r="I1" s="176" t="s">
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="176"/>
-      <c r="K1" s="176"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
       <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="21.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="62"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
-      <c r="H2" s="175"/>
-      <c r="I2" s="177" t="s">
+      <c r="A2" s="198"/>
+      <c r="B2" s="199"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="177"/>
-      <c r="K2" s="177"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
       <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="21.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="178"/>
-      <c r="B3" s="179"/>
-      <c r="C3" s="180" t="s">
+      <c r="A3" s="80"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="180"/>
-      <c r="E3" s="180"/>
-      <c r="F3" s="180"/>
-      <c r="G3" s="180"/>
-      <c r="H3" s="180"/>
-      <c r="I3" s="177" t="s">
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="177"/>
-      <c r="K3" s="177"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="79"/>
       <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="182" t="s">
+      <c r="A4" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="183"/>
-      <c r="C4" s="191"/>
-      <c r="D4" s="191"/>
-      <c r="E4" s="191"/>
-      <c r="F4" s="183"/>
-      <c r="G4" s="183"/>
-      <c r="H4" s="183"/>
-      <c r="I4" s="192"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="192"/>
-      <c r="L4" s="193"/>
+      <c r="B4" s="60"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="92"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+      <c r="L4" s="94"/>
     </row>
     <row r="5" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="182" t="s">
+      <c r="A5" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="183"/>
-      <c r="C5" s="194"/>
-      <c r="D5" s="195"/>
-      <c r="E5" s="195"/>
-      <c r="F5" s="183" t="s">
+      <c r="B5" s="60"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="183"/>
-      <c r="H5" s="183"/>
-      <c r="I5" s="196"/>
-      <c r="J5" s="197"/>
-      <c r="K5" s="196"/>
-      <c r="L5" s="198"/>
+      <c r="G5" s="60"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="63"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="182" t="s">
+      <c r="A6" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="183"/>
-      <c r="C6" s="184"/>
-      <c r="D6" s="185"/>
-      <c r="E6" s="185"/>
-      <c r="F6" s="143" t="s">
+      <c r="B6" s="60"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85"/>
+      <c r="F6" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="143"/>
-      <c r="H6" s="39" t="s">
+      <c r="G6" s="86"/>
+      <c r="H6" s="36" t="s">
         <v>9</v>
       </c>
       <c r="I6" s="5"/>
-      <c r="J6" s="39" t="s">
+      <c r="J6" s="36" t="s">
         <v>59</v>
       </c>
       <c r="K6" s="6"/>
       <c r="L6" s="7"/>
     </row>
     <row r="7" spans="1:12" s="14" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="182" t="s">
+      <c r="A7" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="183" t="s">
+      <c r="B7" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="40"/>
+      <c r="C7" s="37"/>
       <c r="D7" s="8"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
@@ -2996,232 +2992,232 @@
       <c r="L7" s="13"/>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="186" t="s">
+      <c r="A8" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="187"/>
-      <c r="C8" s="187"/>
-      <c r="D8" s="188" t="s">
+      <c r="B8" s="88"/>
+      <c r="C8" s="88"/>
+      <c r="D8" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="189"/>
-      <c r="F8" s="190" t="s">
+      <c r="E8" s="90"/>
+      <c r="F8" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="188"/>
-      <c r="H8" s="188"/>
-      <c r="I8" s="188"/>
-      <c r="J8" s="188"/>
-      <c r="K8" s="189"/>
-      <c r="L8" s="49" t="s">
+      <c r="G8" s="89"/>
+      <c r="H8" s="89"/>
+      <c r="I8" s="89"/>
+      <c r="J8" s="89"/>
+      <c r="K8" s="90"/>
+      <c r="L8" s="46" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="199" t="s">
+      <c r="A9" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="202"/>
-      <c r="C9" s="200"/>
-      <c r="D9" s="201"/>
-      <c r="E9" s="201"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
       <c r="F9" s="75"/>
       <c r="G9" s="75"/>
       <c r="H9" s="75"/>
       <c r="I9" s="75"/>
       <c r="J9" s="75"/>
       <c r="K9" s="75"/>
-      <c r="L9" s="83"/>
+      <c r="L9" s="67"/>
     </row>
     <row r="10" spans="1:12" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="166" t="s">
+      <c r="A10" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="167"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="201"/>
-      <c r="E10" s="201"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="70"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
       <c r="F10" s="75"/>
       <c r="G10" s="75"/>
       <c r="H10" s="75"/>
       <c r="I10" s="75"/>
       <c r="J10" s="75"/>
       <c r="K10" s="75"/>
-      <c r="L10" s="83"/>
+      <c r="L10" s="67"/>
     </row>
     <row r="11" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="96" t="s">
+      <c r="A11" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="101"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="201"/>
-      <c r="E11" s="201"/>
+      <c r="B11" s="72"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
       <c r="F11" s="75"/>
       <c r="G11" s="75"/>
       <c r="H11" s="75"/>
       <c r="I11" s="75"/>
       <c r="J11" s="75"/>
       <c r="K11" s="75"/>
-      <c r="L11" s="83"/>
+      <c r="L11" s="67"/>
     </row>
     <row r="12" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="166" t="s">
+      <c r="A12" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="167"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="201"/>
-      <c r="E12" s="201"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
       <c r="F12" s="75"/>
       <c r="G12" s="75"/>
       <c r="H12" s="75"/>
       <c r="I12" s="75"/>
       <c r="J12" s="75"/>
       <c r="K12" s="75"/>
-      <c r="L12" s="83"/>
+      <c r="L12" s="67"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" s="96" t="s">
+      <c r="A13" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="101"/>
-      <c r="C13" s="97"/>
-      <c r="D13" s="201"/>
-      <c r="E13" s="201"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
       <c r="F13" s="75"/>
       <c r="G13" s="75"/>
       <c r="H13" s="75"/>
       <c r="I13" s="75"/>
       <c r="J13" s="75"/>
       <c r="K13" s="75"/>
-      <c r="L13" s="83"/>
+      <c r="L13" s="67"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14" s="171" t="s">
+      <c r="A14" s="100" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="172"/>
-      <c r="C14" s="173"/>
-      <c r="D14" s="201"/>
-      <c r="E14" s="201"/>
+      <c r="B14" s="101"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
       <c r="F14" s="75"/>
       <c r="G14" s="75"/>
       <c r="H14" s="75"/>
       <c r="I14" s="75"/>
       <c r="J14" s="75"/>
       <c r="K14" s="75"/>
-      <c r="L14" s="83"/>
+      <c r="L14" s="67"/>
     </row>
     <row r="15" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="101"/>
-      <c r="C15" s="97"/>
-      <c r="D15" s="201"/>
-      <c r="E15" s="201"/>
+      <c r="B15" s="72"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
       <c r="F15" s="75"/>
       <c r="G15" s="75"/>
       <c r="H15" s="75"/>
       <c r="I15" s="75"/>
       <c r="J15" s="75"/>
       <c r="K15" s="75"/>
-      <c r="L15" s="83"/>
+      <c r="L15" s="67"/>
     </row>
     <row r="16" spans="1:12" ht="37" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="166" t="s">
+      <c r="A16" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="167"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="201"/>
-      <c r="E16" s="201"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
       <c r="F16" s="75"/>
       <c r="G16" s="75"/>
       <c r="H16" s="75"/>
       <c r="I16" s="75"/>
       <c r="J16" s="75"/>
       <c r="K16" s="75"/>
-      <c r="L16" s="83"/>
+      <c r="L16" s="67"/>
     </row>
     <row r="17" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96" t="s">
+      <c r="A17" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="101"/>
-      <c r="C17" s="97"/>
-      <c r="D17" s="201"/>
-      <c r="E17" s="201"/>
+      <c r="B17" s="72"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
       <c r="F17" s="75"/>
       <c r="G17" s="75"/>
       <c r="H17" s="75"/>
       <c r="I17" s="75"/>
       <c r="J17" s="75"/>
       <c r="K17" s="75"/>
-      <c r="L17" s="83"/>
+      <c r="L17" s="67"/>
     </row>
     <row r="18" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="166" t="s">
+      <c r="A18" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="167"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="201"/>
-      <c r="E18" s="201"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="70"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
       <c r="F18" s="75"/>
       <c r="G18" s="75"/>
       <c r="H18" s="75"/>
       <c r="I18" s="75"/>
       <c r="J18" s="75"/>
       <c r="K18" s="75"/>
-      <c r="L18" s="83"/>
+      <c r="L18" s="67"/>
     </row>
     <row r="19" spans="1:12" ht="32" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="168" t="s">
+      <c r="A19" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="169"/>
-      <c r="C19" s="170"/>
-      <c r="D19" s="203"/>
-      <c r="E19" s="203"/>
-      <c r="F19" s="204"/>
-      <c r="G19" s="204"/>
-      <c r="H19" s="204"/>
-      <c r="I19" s="204"/>
-      <c r="J19" s="204"/>
-      <c r="K19" s="204"/>
-      <c r="L19" s="38"/>
+      <c r="B19" s="96"/>
+      <c r="C19" s="97"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="99"/>
+      <c r="H19" s="99"/>
+      <c r="I19" s="99"/>
+      <c r="J19" s="99"/>
+      <c r="K19" s="99"/>
+      <c r="L19" s="35"/>
     </row>
     <row r="20" spans="1:12" s="15" customFormat="1" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="98" t="s">
+      <c r="A20" s="194" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="181"/>
-      <c r="C20" s="32" t="s">
+      <c r="B20" s="202"/>
+      <c r="C20" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="D20" s="67" t="s">
+      <c r="D20" s="176" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="68"/>
-      <c r="F20" s="46" t="s">
+      <c r="E20" s="70"/>
+      <c r="F20" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="G20" s="33" t="s">
+      <c r="G20" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="H20" s="46" t="s">
+      <c r="H20" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="I20" s="47" t="s">
+      <c r="I20" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="J20" s="164" t="s">
+      <c r="J20" s="200" t="s">
         <v>21</v>
       </c>
-      <c r="K20" s="165"/>
-      <c r="L20" s="48" t="s">
+      <c r="K20" s="201"/>
+      <c r="L20" s="45" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3229,19 +3225,20 @@
       <c r="A21" s="16">
         <v>1</v>
       </c>
-      <c r="B21" s="34"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="70"/>
+      <c r="B21" s="203"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="108"/>
       <c r="F21" s="17"/>
-      <c r="G21" s="31"/>
+      <c r="G21" s="30"/>
       <c r="H21" s="18"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="64">
+      <c r="I21" s="57"/>
+      <c r="J21" s="103">
         <v>0</v>
       </c>
-      <c r="K21" s="65"/>
-      <c r="L21" s="20">
+      <c r="K21" s="104"/>
+      <c r="L21" s="19">
+        <f>G21*H21</f>
         <v>0</v>
       </c>
     </row>
@@ -3249,19 +3246,20 @@
       <c r="A22" s="16">
         <v>2</v>
       </c>
-      <c r="B22" s="35"/>
+      <c r="B22" s="33"/>
       <c r="C22" s="17"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="70"/>
+      <c r="D22" s="107"/>
+      <c r="E22" s="108"/>
       <c r="F22" s="17"/>
-      <c r="G22" s="31"/>
+      <c r="G22" s="30"/>
       <c r="H22" s="18"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="64">
+      <c r="I22" s="57"/>
+      <c r="J22" s="103">
         <v>0</v>
       </c>
-      <c r="K22" s="65"/>
-      <c r="L22" s="20">
+      <c r="K22" s="104"/>
+      <c r="L22" s="19">
+        <f t="shared" ref="L22:L41" si="0">G22*H22</f>
         <v>0</v>
       </c>
     </row>
@@ -3269,19 +3267,20 @@
       <c r="A23" s="16">
         <v>3</v>
       </c>
-      <c r="B23" s="35"/>
+      <c r="B23" s="33"/>
       <c r="C23" s="17"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="70"/>
+      <c r="D23" s="107"/>
+      <c r="E23" s="108"/>
       <c r="F23" s="17"/>
-      <c r="G23" s="31"/>
+      <c r="G23" s="30"/>
       <c r="H23" s="18"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="64">
+      <c r="I23" s="57"/>
+      <c r="J23" s="103">
         <v>0</v>
       </c>
-      <c r="K23" s="65"/>
-      <c r="L23" s="20">
+      <c r="K23" s="104"/>
+      <c r="L23" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3289,19 +3288,20 @@
       <c r="A24" s="16">
         <v>4</v>
       </c>
-      <c r="B24" s="35"/>
+      <c r="B24" s="33"/>
       <c r="C24" s="17"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="70"/>
+      <c r="D24" s="107"/>
+      <c r="E24" s="108"/>
       <c r="F24" s="17"/>
-      <c r="G24" s="31"/>
+      <c r="G24" s="30"/>
       <c r="H24" s="18"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="64">
+      <c r="I24" s="57"/>
+      <c r="J24" s="103">
         <v>0</v>
       </c>
-      <c r="K24" s="65"/>
-      <c r="L24" s="20">
+      <c r="K24" s="104"/>
+      <c r="L24" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3309,19 +3309,20 @@
       <c r="A25" s="16">
         <v>5</v>
       </c>
-      <c r="B25" s="35"/>
+      <c r="B25" s="33"/>
       <c r="C25" s="17"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="70"/>
+      <c r="D25" s="107"/>
+      <c r="E25" s="108"/>
       <c r="F25" s="17"/>
-      <c r="G25" s="31"/>
+      <c r="G25" s="30"/>
       <c r="H25" s="18"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="64">
+      <c r="I25" s="57"/>
+      <c r="J25" s="103">
         <v>0</v>
       </c>
-      <c r="K25" s="65"/>
-      <c r="L25" s="20">
+      <c r="K25" s="104"/>
+      <c r="L25" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3329,19 +3330,20 @@
       <c r="A26" s="16">
         <v>6</v>
       </c>
-      <c r="B26" s="35"/>
+      <c r="B26" s="33"/>
       <c r="C26" s="17"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="70"/>
+      <c r="D26" s="107"/>
+      <c r="E26" s="108"/>
       <c r="F26" s="17"/>
-      <c r="G26" s="31"/>
+      <c r="G26" s="30"/>
       <c r="H26" s="18"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="64">
+      <c r="I26" s="57"/>
+      <c r="J26" s="103">
         <v>0</v>
       </c>
-      <c r="K26" s="65"/>
-      <c r="L26" s="20">
+      <c r="K26" s="104"/>
+      <c r="L26" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3349,19 +3351,20 @@
       <c r="A27" s="16">
         <v>7</v>
       </c>
-      <c r="B27" s="35"/>
+      <c r="B27" s="33"/>
       <c r="C27" s="17"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="70"/>
+      <c r="D27" s="107"/>
+      <c r="E27" s="108"/>
       <c r="F27" s="17"/>
-      <c r="G27" s="31"/>
+      <c r="G27" s="30"/>
       <c r="H27" s="18"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="64">
+      <c r="I27" s="57"/>
+      <c r="J27" s="103">
         <v>0</v>
       </c>
-      <c r="K27" s="65"/>
-      <c r="L27" s="20">
+      <c r="K27" s="104"/>
+      <c r="L27" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3369,19 +3372,20 @@
       <c r="A28" s="16">
         <v>8</v>
       </c>
-      <c r="B28" s="35"/>
+      <c r="B28" s="33"/>
       <c r="C28" s="17"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="70"/>
+      <c r="D28" s="107"/>
+      <c r="E28" s="108"/>
       <c r="F28" s="17"/>
-      <c r="G28" s="31"/>
+      <c r="G28" s="30"/>
       <c r="H28" s="18"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="64">
+      <c r="I28" s="57"/>
+      <c r="J28" s="103">
         <v>0</v>
       </c>
-      <c r="K28" s="65"/>
-      <c r="L28" s="20">
+      <c r="K28" s="104"/>
+      <c r="L28" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3389,19 +3393,20 @@
       <c r="A29" s="16">
         <v>9</v>
       </c>
-      <c r="B29" s="35"/>
+      <c r="B29" s="33"/>
       <c r="C29" s="17"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="70"/>
+      <c r="D29" s="107"/>
+      <c r="E29" s="108"/>
       <c r="F29" s="17"/>
-      <c r="G29" s="31"/>
+      <c r="G29" s="30"/>
       <c r="H29" s="18"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="64">
+      <c r="I29" s="57"/>
+      <c r="J29" s="103">
         <v>0</v>
       </c>
-      <c r="K29" s="65"/>
-      <c r="L29" s="20">
+      <c r="K29" s="104"/>
+      <c r="L29" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3409,19 +3414,20 @@
       <c r="A30" s="16">
         <v>10</v>
       </c>
-      <c r="B30" s="35"/>
+      <c r="B30" s="33"/>
       <c r="C30" s="17"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="70"/>
+      <c r="D30" s="107"/>
+      <c r="E30" s="108"/>
       <c r="F30" s="17"/>
-      <c r="G30" s="31"/>
+      <c r="G30" s="30"/>
       <c r="H30" s="18"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="64">
+      <c r="I30" s="57"/>
+      <c r="J30" s="103">
         <v>0</v>
       </c>
-      <c r="K30" s="65"/>
-      <c r="L30" s="20">
+      <c r="K30" s="104"/>
+      <c r="L30" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3429,19 +3435,20 @@
       <c r="A31" s="16">
         <v>11</v>
       </c>
-      <c r="B31" s="35"/>
+      <c r="B31" s="33"/>
       <c r="C31" s="17"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="70"/>
+      <c r="D31" s="107"/>
+      <c r="E31" s="108"/>
       <c r="F31" s="17"/>
-      <c r="G31" s="31"/>
+      <c r="G31" s="30"/>
       <c r="H31" s="18"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="64">
+      <c r="I31" s="57"/>
+      <c r="J31" s="103">
         <v>0</v>
       </c>
-      <c r="K31" s="65"/>
-      <c r="L31" s="20">
+      <c r="K31" s="104"/>
+      <c r="L31" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3449,19 +3456,20 @@
       <c r="A32" s="16">
         <v>12</v>
       </c>
-      <c r="B32" s="35"/>
+      <c r="B32" s="33"/>
       <c r="C32" s="17"/>
-      <c r="D32" s="69"/>
-      <c r="E32" s="70"/>
+      <c r="D32" s="107"/>
+      <c r="E32" s="108"/>
       <c r="F32" s="17"/>
-      <c r="G32" s="31"/>
+      <c r="G32" s="30"/>
       <c r="H32" s="18"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="64">
+      <c r="I32" s="57"/>
+      <c r="J32" s="103">
         <v>0</v>
       </c>
-      <c r="K32" s="65"/>
-      <c r="L32" s="20">
+      <c r="K32" s="104"/>
+      <c r="L32" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3469,19 +3477,20 @@
       <c r="A33" s="16">
         <v>13</v>
       </c>
-      <c r="B33" s="35"/>
+      <c r="B33" s="33"/>
       <c r="C33" s="17"/>
-      <c r="D33" s="69"/>
-      <c r="E33" s="70"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="108"/>
       <c r="F33" s="17"/>
-      <c r="G33" s="31"/>
+      <c r="G33" s="30"/>
       <c r="H33" s="18"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="64">
+      <c r="I33" s="57"/>
+      <c r="J33" s="103">
         <v>0</v>
       </c>
-      <c r="K33" s="65"/>
-      <c r="L33" s="20">
+      <c r="K33" s="104"/>
+      <c r="L33" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3489,19 +3498,20 @@
       <c r="A34" s="16">
         <v>14</v>
       </c>
-      <c r="B34" s="35"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="17"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="70"/>
+      <c r="D34" s="107"/>
+      <c r="E34" s="108"/>
       <c r="F34" s="17"/>
-      <c r="G34" s="31"/>
+      <c r="G34" s="30"/>
       <c r="H34" s="18"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="64">
+      <c r="I34" s="57"/>
+      <c r="J34" s="103">
         <v>0</v>
       </c>
-      <c r="K34" s="65"/>
-      <c r="L34" s="20">
+      <c r="K34" s="104"/>
+      <c r="L34" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3509,19 +3519,20 @@
       <c r="A35" s="16">
         <v>15</v>
       </c>
-      <c r="B35" s="35"/>
+      <c r="B35" s="33"/>
       <c r="C35" s="17"/>
-      <c r="D35" s="69"/>
-      <c r="E35" s="70"/>
+      <c r="D35" s="107"/>
+      <c r="E35" s="108"/>
       <c r="F35" s="17"/>
-      <c r="G35" s="31"/>
+      <c r="G35" s="30"/>
       <c r="H35" s="18"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="64">
+      <c r="I35" s="57"/>
+      <c r="J35" s="103">
         <v>0</v>
       </c>
-      <c r="K35" s="65"/>
-      <c r="L35" s="20">
+      <c r="K35" s="104"/>
+      <c r="L35" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3529,19 +3540,20 @@
       <c r="A36" s="16">
         <v>16</v>
       </c>
-      <c r="B36" s="35"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="17"/>
-      <c r="D36" s="69"/>
-      <c r="E36" s="70"/>
+      <c r="D36" s="107"/>
+      <c r="E36" s="108"/>
       <c r="F36" s="17"/>
-      <c r="G36" s="31"/>
+      <c r="G36" s="30"/>
       <c r="H36" s="18"/>
-      <c r="I36" s="19"/>
-      <c r="J36" s="64">
+      <c r="I36" s="57"/>
+      <c r="J36" s="103">
         <v>0</v>
       </c>
-      <c r="K36" s="65"/>
-      <c r="L36" s="20">
+      <c r="K36" s="104"/>
+      <c r="L36" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3549,19 +3561,20 @@
       <c r="A37" s="16">
         <v>17</v>
       </c>
-      <c r="B37" s="35"/>
+      <c r="B37" s="33"/>
       <c r="C37" s="17"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="70"/>
+      <c r="D37" s="107"/>
+      <c r="E37" s="108"/>
       <c r="F37" s="17"/>
-      <c r="G37" s="31"/>
+      <c r="G37" s="30"/>
       <c r="H37" s="18"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="64">
+      <c r="I37" s="57"/>
+      <c r="J37" s="103">
         <v>0</v>
       </c>
-      <c r="K37" s="65"/>
-      <c r="L37" s="20">
+      <c r="K37" s="104"/>
+      <c r="L37" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3569,19 +3582,20 @@
       <c r="A38" s="16">
         <v>18</v>
       </c>
-      <c r="B38" s="35"/>
+      <c r="B38" s="33"/>
       <c r="C38" s="17"/>
-      <c r="D38" s="69"/>
-      <c r="E38" s="70"/>
+      <c r="D38" s="107"/>
+      <c r="E38" s="108"/>
       <c r="F38" s="17"/>
-      <c r="G38" s="31"/>
+      <c r="G38" s="30"/>
       <c r="H38" s="18"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="64">
+      <c r="I38" s="57"/>
+      <c r="J38" s="103">
         <v>0</v>
       </c>
-      <c r="K38" s="65"/>
-      <c r="L38" s="20">
+      <c r="K38" s="104"/>
+      <c r="L38" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3589,19 +3603,20 @@
       <c r="A39" s="16">
         <v>19</v>
       </c>
-      <c r="B39" s="35"/>
+      <c r="B39" s="33"/>
       <c r="C39" s="17"/>
-      <c r="D39" s="69"/>
-      <c r="E39" s="70"/>
+      <c r="D39" s="107"/>
+      <c r="E39" s="108"/>
       <c r="F39" s="17"/>
-      <c r="G39" s="31"/>
+      <c r="G39" s="30"/>
       <c r="H39" s="18"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="64">
+      <c r="I39" s="57"/>
+      <c r="J39" s="103">
         <v>0</v>
       </c>
-      <c r="K39" s="65"/>
-      <c r="L39" s="20">
+      <c r="K39" s="104"/>
+      <c r="L39" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -3609,628 +3624,536 @@
       <c r="A40" s="16">
         <v>20</v>
       </c>
-      <c r="B40" s="35"/>
+      <c r="B40" s="33"/>
       <c r="C40" s="17"/>
-      <c r="D40" s="69"/>
-      <c r="E40" s="70"/>
+      <c r="D40" s="107"/>
+      <c r="E40" s="108"/>
       <c r="F40" s="17"/>
-      <c r="G40" s="31"/>
+      <c r="G40" s="30"/>
       <c r="H40" s="18"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="64">
+      <c r="I40" s="57"/>
+      <c r="J40" s="103">
         <v>0</v>
       </c>
-      <c r="K40" s="65"/>
-      <c r="L40" s="20">
+      <c r="K40" s="104"/>
+      <c r="L40" s="19">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:12" s="14" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="54">
+      <c r="A41" s="51">
         <v>21</v>
       </c>
-      <c r="B41" s="37"/>
-      <c r="C41" s="55"/>
-      <c r="D41" s="162"/>
-      <c r="E41" s="163"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="160">
+      <c r="B41" s="34"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="109"/>
+      <c r="E41" s="110"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="53"/>
+      <c r="H41" s="54"/>
+      <c r="I41" s="56"/>
+      <c r="J41" s="105">
         <v>0</v>
       </c>
-      <c r="K41" s="161"/>
-      <c r="L41" s="50">
+      <c r="K41" s="106"/>
+      <c r="L41" s="47">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:12" s="14" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="138" t="s">
+      <c r="A42" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="B42" s="139"/>
-      <c r="C42" s="139"/>
-      <c r="D42" s="139"/>
-      <c r="E42" s="139"/>
-      <c r="F42" s="139"/>
-      <c r="G42" s="139"/>
-      <c r="H42" s="139"/>
-      <c r="I42" s="140"/>
-      <c r="J42" s="141" t="s">
+      <c r="B42" s="112"/>
+      <c r="C42" s="112"/>
+      <c r="D42" s="112"/>
+      <c r="E42" s="112"/>
+      <c r="F42" s="112"/>
+      <c r="G42" s="112"/>
+      <c r="H42" s="112"/>
+      <c r="I42" s="113"/>
+      <c r="J42" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="K42" s="142"/>
-      <c r="L42" s="51" t="s">
+      <c r="K42" s="115"/>
+      <c r="L42" s="48">
+        <f>SUM(L21:L41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="55" t="s">
+        <v>24</v>
+      </c>
+      <c r="B43" s="86" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="86"/>
+      <c r="D43" s="86"/>
+      <c r="E43" s="86"/>
+      <c r="F43" s="86"/>
+      <c r="G43" s="86"/>
+      <c r="H43" s="86"/>
+      <c r="I43" s="116"/>
+      <c r="J43" s="119" t="s">
+        <v>26</v>
+      </c>
+      <c r="K43" s="120"/>
+      <c r="L43" s="121"/>
+    </row>
+    <row r="44" spans="1:12" s="14" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="38"/>
+      <c r="B44" s="117"/>
+      <c r="C44" s="117"/>
+      <c r="D44" s="117"/>
+      <c r="E44" s="117"/>
+      <c r="F44" s="117"/>
+      <c r="G44" s="117"/>
+      <c r="H44" s="117"/>
+      <c r="I44" s="118"/>
+      <c r="J44" s="122"/>
+      <c r="K44" s="123"/>
+      <c r="L44" s="124"/>
+    </row>
+    <row r="45" spans="1:12" s="14" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="125" t="s">
+        <v>27</v>
+      </c>
+      <c r="B45" s="126"/>
+      <c r="C45" s="126"/>
+      <c r="D45" s="126"/>
+      <c r="E45" s="126"/>
+      <c r="F45" s="126"/>
+      <c r="G45" s="126"/>
+      <c r="H45" s="126"/>
+      <c r="I45" s="126"/>
+      <c r="J45" s="126"/>
+      <c r="K45" s="126"/>
+      <c r="L45" s="127"/>
+    </row>
+    <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" s="72"/>
+      <c r="C46" s="73"/>
+      <c r="D46" s="128" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="72"/>
+      <c r="F46" s="72"/>
+      <c r="G46" s="72"/>
+      <c r="H46" s="72"/>
+      <c r="I46" s="72"/>
+      <c r="J46" s="72"/>
+      <c r="K46" s="73"/>
+      <c r="L46" s="129" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="131" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" s="132"/>
+      <c r="C47" s="132"/>
+      <c r="D47" s="133" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47" s="132"/>
+      <c r="F47" s="132"/>
+      <c r="G47" s="132"/>
+      <c r="H47" s="132"/>
+      <c r="I47" s="132"/>
+      <c r="J47" s="132"/>
+      <c r="K47" s="134"/>
+      <c r="L47" s="130"/>
+    </row>
+    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="135"/>
+      <c r="B48" s="136"/>
+      <c r="C48" s="137"/>
+      <c r="D48" s="141"/>
+      <c r="E48" s="142"/>
+      <c r="F48" s="142"/>
+      <c r="G48" s="142"/>
+      <c r="H48" s="142"/>
+      <c r="I48" s="142"/>
+      <c r="J48" s="142"/>
+      <c r="K48" s="143"/>
+      <c r="L48" s="147"/>
+    </row>
+    <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="138"/>
+      <c r="B49" s="139"/>
+      <c r="C49" s="140"/>
+      <c r="D49" s="144"/>
+      <c r="E49" s="145"/>
+      <c r="F49" s="145"/>
+      <c r="G49" s="145"/>
+      <c r="H49" s="145"/>
+      <c r="I49" s="145"/>
+      <c r="J49" s="145"/>
+      <c r="K49" s="146"/>
+      <c r="L49" s="147"/>
+    </row>
+    <row r="50" spans="1:12" ht="43" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="B50" s="149"/>
+      <c r="C50" s="149"/>
+      <c r="D50" s="149"/>
+      <c r="E50" s="149"/>
+      <c r="F50" s="149"/>
+      <c r="G50" s="149"/>
+      <c r="H50" s="149"/>
+      <c r="I50" s="149"/>
+      <c r="J50" s="149"/>
+      <c r="K50" s="149"/>
+      <c r="L50" s="150"/>
+    </row>
+    <row r="51" spans="1:12" ht="32" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="151" t="s">
+        <v>33</v>
+      </c>
+      <c r="B51" s="149"/>
+      <c r="C51" s="149"/>
+      <c r="D51" s="149"/>
+      <c r="E51" s="149"/>
+      <c r="F51" s="149"/>
+      <c r="G51" s="149"/>
+      <c r="H51" s="149"/>
+      <c r="I51" s="149"/>
+      <c r="J51" s="149"/>
+      <c r="K51" s="149"/>
+      <c r="L51" s="150"/>
+    </row>
+    <row r="52" spans="1:12" s="14" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="152" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" s="153"/>
+      <c r="C52" s="153"/>
+      <c r="D52" s="154"/>
+      <c r="E52" s="155"/>
+      <c r="F52" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G52" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="H52" s="153" t="s">
+        <v>37</v>
+      </c>
+      <c r="I52" s="153"/>
+      <c r="J52" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="K52" s="153" t="s">
+        <v>39</v>
+      </c>
+      <c r="L52" s="158"/>
+    </row>
+    <row r="53" spans="1:12" s="14" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="159" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="160"/>
+      <c r="C53" s="160"/>
+      <c r="D53" s="161"/>
+      <c r="E53" s="156"/>
+      <c r="F53" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G53" s="22"/>
+      <c r="H53" s="163"/>
+      <c r="I53" s="163"/>
+      <c r="J53" s="23"/>
+      <c r="K53" s="163"/>
+      <c r="L53" s="164"/>
+    </row>
+    <row r="54" spans="1:12" s="14" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="159"/>
+      <c r="B54" s="160"/>
+      <c r="C54" s="160"/>
+      <c r="D54" s="162"/>
+      <c r="E54" s="156"/>
+      <c r="F54" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="G54" s="22"/>
+      <c r="H54" s="163"/>
+      <c r="I54" s="163"/>
+      <c r="J54" s="23"/>
+      <c r="K54" s="163"/>
+      <c r="L54" s="164"/>
+    </row>
+    <row r="55" spans="1:12" s="24" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="165" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="166"/>
+      <c r="C55" s="166"/>
+      <c r="D55" s="162"/>
+      <c r="E55" s="156"/>
+      <c r="F55" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="G55" s="22"/>
+      <c r="H55" s="163"/>
+      <c r="I55" s="163"/>
+      <c r="J55" s="23"/>
+      <c r="K55" s="163"/>
+      <c r="L55" s="164"/>
+    </row>
+    <row r="56" spans="1:12" s="14" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="165"/>
+      <c r="B56" s="166"/>
+      <c r="C56" s="166"/>
+      <c r="D56" s="162"/>
+      <c r="E56" s="156"/>
+      <c r="F56" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G56" s="22"/>
+      <c r="H56" s="163"/>
+      <c r="I56" s="163"/>
+      <c r="J56" s="23"/>
+      <c r="K56" s="163"/>
+      <c r="L56" s="164"/>
+    </row>
+    <row r="57" spans="1:12" s="14" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="159" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="160"/>
+      <c r="C57" s="160"/>
+      <c r="D57" s="162"/>
+      <c r="E57" s="156"/>
+      <c r="F57" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G57" s="22"/>
+      <c r="H57" s="163"/>
+      <c r="I57" s="163"/>
+      <c r="J57" s="23"/>
+      <c r="K57" s="163"/>
+      <c r="L57" s="164"/>
+    </row>
+    <row r="58" spans="1:12" s="14" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="159"/>
+      <c r="B58" s="160"/>
+      <c r="C58" s="160"/>
+      <c r="D58" s="162"/>
+      <c r="E58" s="156"/>
+      <c r="F58" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="G58" s="22"/>
+      <c r="H58" s="163"/>
+      <c r="I58" s="163"/>
+      <c r="J58" s="23"/>
+      <c r="K58" s="163"/>
+      <c r="L58" s="164"/>
+    </row>
+    <row r="59" spans="1:12" s="14" customFormat="1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="159" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="160"/>
+      <c r="C59" s="160"/>
+      <c r="D59" s="171"/>
+      <c r="E59" s="156"/>
+      <c r="F59" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G59" s="22"/>
+      <c r="H59" s="163"/>
+      <c r="I59" s="163"/>
+      <c r="J59" s="23"/>
+      <c r="K59" s="163"/>
+      <c r="L59" s="164"/>
+    </row>
+    <row r="60" spans="1:12" s="14" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="169"/>
+      <c r="B60" s="170"/>
+      <c r="C60" s="170"/>
+      <c r="D60" s="172"/>
+      <c r="E60" s="157"/>
+      <c r="F60" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="G60" s="50"/>
+      <c r="H60" s="173" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" s="14" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="59" t="s">
-        <v>24</v>
-      </c>
-      <c r="B43" s="143" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="143"/>
-      <c r="D43" s="143"/>
-      <c r="E43" s="143"/>
-      <c r="F43" s="143"/>
-      <c r="G43" s="143"/>
-      <c r="H43" s="143"/>
-      <c r="I43" s="144"/>
-      <c r="J43" s="147" t="s">
-        <v>26</v>
-      </c>
-      <c r="K43" s="148"/>
-      <c r="L43" s="149"/>
-    </row>
-    <row r="44" spans="1:12" s="14" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="41"/>
-      <c r="B44" s="145"/>
-      <c r="C44" s="145"/>
-      <c r="D44" s="145"/>
-      <c r="E44" s="145"/>
-      <c r="F44" s="145"/>
-      <c r="G44" s="145"/>
-      <c r="H44" s="145"/>
-      <c r="I44" s="146"/>
-      <c r="J44" s="150"/>
-      <c r="K44" s="151"/>
-      <c r="L44" s="152"/>
-    </row>
-    <row r="45" spans="1:12" s="14" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="153" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" s="154"/>
-      <c r="C45" s="154"/>
-      <c r="D45" s="154"/>
-      <c r="E45" s="154"/>
-      <c r="F45" s="154"/>
-      <c r="G45" s="154"/>
-      <c r="H45" s="154"/>
-      <c r="I45" s="154"/>
-      <c r="J45" s="154"/>
-      <c r="K45" s="154"/>
-      <c r="L45" s="155"/>
-    </row>
-    <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="96" t="s">
+      <c r="I60" s="173"/>
+      <c r="J60" s="50"/>
+      <c r="K60" s="173" t="s">
+        <v>61</v>
+      </c>
+      <c r="L60" s="174"/>
+    </row>
+    <row r="61" spans="1:12" s="14" customFormat="1" ht="8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="39"/>
+      <c r="B61" s="37"/>
+      <c r="C61" s="37"/>
+      <c r="D61" s="37"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="39"/>
+      <c r="G61" s="40"/>
+      <c r="H61" s="41"/>
+      <c r="I61" s="42"/>
+      <c r="J61" s="42"/>
+      <c r="K61" s="42"/>
+      <c r="L61" s="42"/>
+    </row>
+    <row r="62" spans="1:12" s="14" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="191" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="192"/>
+      <c r="C62" s="192"/>
+      <c r="D62" s="192"/>
+      <c r="E62" s="192"/>
+      <c r="F62" s="192"/>
+      <c r="G62" s="192"/>
+      <c r="H62" s="192"/>
+      <c r="I62" s="192"/>
+      <c r="J62" s="192"/>
+      <c r="K62" s="192"/>
+      <c r="L62" s="193"/>
+    </row>
+    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="71"/>
+      <c r="B63" s="73"/>
+      <c r="C63" s="128" t="s">
         <v>28</v>
       </c>
-      <c r="B46" s="101"/>
-      <c r="C46" s="97"/>
-      <c r="D46" s="100" t="s">
+      <c r="D63" s="73"/>
+      <c r="E63" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="E46" s="101"/>
-      <c r="F46" s="101"/>
-      <c r="G46" s="101"/>
-      <c r="H46" s="101"/>
-      <c r="I46" s="101"/>
-      <c r="J46" s="101"/>
-      <c r="K46" s="97"/>
-      <c r="L46" s="102" t="s">
+      <c r="F63" s="72"/>
+      <c r="G63" s="72"/>
+      <c r="H63" s="72"/>
+      <c r="I63" s="72"/>
+      <c r="J63" s="72"/>
+      <c r="K63" s="73"/>
+      <c r="L63" s="129" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="156" t="s">
+    <row r="64" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="194"/>
+      <c r="B64" s="195"/>
+      <c r="C64" s="167" t="s">
         <v>30</v>
       </c>
-      <c r="B47" s="157"/>
-      <c r="C47" s="157"/>
-      <c r="D47" s="158" t="s">
+      <c r="D64" s="168"/>
+      <c r="E64" s="167" t="s">
         <v>31</v>
       </c>
-      <c r="E47" s="157"/>
-      <c r="F47" s="157"/>
-      <c r="G47" s="157"/>
-      <c r="H47" s="157"/>
-      <c r="I47" s="157"/>
-      <c r="J47" s="157"/>
-      <c r="K47" s="159"/>
-      <c r="L47" s="103"/>
-    </row>
-    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="117"/>
-      <c r="B48" s="118"/>
-      <c r="C48" s="119"/>
-      <c r="D48" s="76"/>
-      <c r="E48" s="77"/>
-      <c r="F48" s="77"/>
-      <c r="G48" s="77"/>
-      <c r="H48" s="77"/>
-      <c r="I48" s="77"/>
-      <c r="J48" s="77"/>
-      <c r="K48" s="78"/>
-      <c r="L48" s="123"/>
-    </row>
-    <row r="49" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="120"/>
-      <c r="B49" s="121"/>
-      <c r="C49" s="122"/>
-      <c r="D49" s="79"/>
-      <c r="E49" s="80"/>
-      <c r="F49" s="80"/>
-      <c r="G49" s="80"/>
-      <c r="H49" s="80"/>
-      <c r="I49" s="80"/>
-      <c r="J49" s="80"/>
-      <c r="K49" s="81"/>
-      <c r="L49" s="123"/>
-    </row>
-    <row r="50" spans="1:12" ht="43" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="124" t="s">
-        <v>32</v>
-      </c>
-      <c r="B50" s="125"/>
-      <c r="C50" s="125"/>
-      <c r="D50" s="125"/>
-      <c r="E50" s="125"/>
-      <c r="F50" s="125"/>
-      <c r="G50" s="125"/>
-      <c r="H50" s="125"/>
-      <c r="I50" s="125"/>
-      <c r="J50" s="125"/>
-      <c r="K50" s="125"/>
-      <c r="L50" s="126"/>
-    </row>
-    <row r="51" spans="1:12" ht="32" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="127" t="s">
-        <v>33</v>
-      </c>
-      <c r="B51" s="125"/>
-      <c r="C51" s="125"/>
-      <c r="D51" s="125"/>
-      <c r="E51" s="125"/>
-      <c r="F51" s="125"/>
-      <c r="G51" s="125"/>
-      <c r="H51" s="125"/>
-      <c r="I51" s="125"/>
-      <c r="J51" s="125"/>
-      <c r="K51" s="125"/>
-      <c r="L51" s="126"/>
-    </row>
-    <row r="52" spans="1:12" s="14" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="128" t="s">
-        <v>34</v>
-      </c>
-      <c r="B52" s="129"/>
-      <c r="C52" s="129"/>
-      <c r="D52" s="130"/>
-      <c r="E52" s="131"/>
-      <c r="F52" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="G52" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="H52" s="129" t="s">
-        <v>37</v>
-      </c>
-      <c r="I52" s="129"/>
-      <c r="J52" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="K52" s="129" t="s">
-        <v>39</v>
-      </c>
-      <c r="L52" s="134"/>
-    </row>
-    <row r="53" spans="1:12" s="14" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="106" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="107"/>
-      <c r="C53" s="107"/>
-      <c r="D53" s="135"/>
-      <c r="E53" s="132"/>
-      <c r="F53" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G53" s="23"/>
-      <c r="H53" s="112"/>
-      <c r="I53" s="112"/>
-      <c r="J53" s="24"/>
-      <c r="K53" s="112"/>
-      <c r="L53" s="113"/>
-    </row>
-    <row r="54" spans="1:12" s="14" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="106"/>
-      <c r="B54" s="107"/>
-      <c r="C54" s="107"/>
-      <c r="D54" s="116"/>
-      <c r="E54" s="132"/>
-      <c r="F54" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="G54" s="23"/>
-      <c r="H54" s="112"/>
-      <c r="I54" s="112"/>
-      <c r="J54" s="24"/>
-      <c r="K54" s="112"/>
-      <c r="L54" s="113"/>
-    </row>
-    <row r="55" spans="1:12" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="136" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="137"/>
-      <c r="C55" s="137"/>
-      <c r="D55" s="116"/>
-      <c r="E55" s="132"/>
-      <c r="F55" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="G55" s="23"/>
-      <c r="H55" s="112"/>
-      <c r="I55" s="112"/>
-      <c r="J55" s="24"/>
-      <c r="K55" s="112"/>
-      <c r="L55" s="113"/>
-    </row>
-    <row r="56" spans="1:12" s="14" customFormat="1" ht="11.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="136"/>
-      <c r="B56" s="137"/>
-      <c r="C56" s="137"/>
-      <c r="D56" s="116"/>
-      <c r="E56" s="132"/>
-      <c r="F56" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="G56" s="23"/>
-      <c r="H56" s="112"/>
-      <c r="I56" s="112"/>
-      <c r="J56" s="24"/>
-      <c r="K56" s="112"/>
-      <c r="L56" s="113"/>
-    </row>
-    <row r="57" spans="1:12" s="14" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="106" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="107"/>
-      <c r="C57" s="107"/>
-      <c r="D57" s="116"/>
-      <c r="E57" s="132"/>
-      <c r="F57" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="G57" s="23"/>
-      <c r="H57" s="112"/>
-      <c r="I57" s="112"/>
-      <c r="J57" s="24"/>
-      <c r="K57" s="112"/>
-      <c r="L57" s="113"/>
-    </row>
-    <row r="58" spans="1:12" s="14" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="106"/>
-      <c r="B58" s="107"/>
-      <c r="C58" s="107"/>
-      <c r="D58" s="116"/>
-      <c r="E58" s="132"/>
-      <c r="F58" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="G58" s="23"/>
-      <c r="H58" s="112"/>
-      <c r="I58" s="112"/>
-      <c r="J58" s="24"/>
-      <c r="K58" s="112"/>
-      <c r="L58" s="113"/>
-    </row>
-    <row r="59" spans="1:12" s="14" customFormat="1" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="106" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="107"/>
-      <c r="C59" s="107"/>
-      <c r="D59" s="110"/>
-      <c r="E59" s="132"/>
-      <c r="F59" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="G59" s="23"/>
-      <c r="H59" s="112"/>
-      <c r="I59" s="112"/>
-      <c r="J59" s="24"/>
-      <c r="K59" s="112"/>
-      <c r="L59" s="113"/>
-    </row>
-    <row r="60" spans="1:12" s="14" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="108"/>
-      <c r="B60" s="109"/>
-      <c r="C60" s="109"/>
-      <c r="D60" s="111"/>
-      <c r="E60" s="133"/>
-      <c r="F60" s="52" t="s">
-        <v>44</v>
-      </c>
-      <c r="G60" s="53"/>
-      <c r="H60" s="114" t="s">
-        <v>61</v>
-      </c>
-      <c r="I60" s="114"/>
-      <c r="J60" s="53"/>
-      <c r="K60" s="114" t="s">
-        <v>61</v>
-      </c>
-      <c r="L60" s="115"/>
-    </row>
-    <row r="61" spans="1:12" s="14" customFormat="1" ht="8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="42"/>
-      <c r="B61" s="40"/>
-      <c r="C61" s="40"/>
-      <c r="D61" s="40"/>
-      <c r="E61" s="42"/>
-      <c r="F61" s="42"/>
-      <c r="G61" s="43"/>
-      <c r="H61" s="44"/>
-      <c r="I61" s="45"/>
-      <c r="J61" s="45"/>
-      <c r="K61" s="45"/>
-      <c r="L61" s="45"/>
-    </row>
-    <row r="62" spans="1:12" s="14" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="93" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" s="94"/>
-      <c r="C62" s="94"/>
-      <c r="D62" s="94"/>
-      <c r="E62" s="94"/>
-      <c r="F62" s="94"/>
-      <c r="G62" s="94"/>
-      <c r="H62" s="94"/>
-      <c r="I62" s="94"/>
-      <c r="J62" s="94"/>
-      <c r="K62" s="94"/>
-      <c r="L62" s="95"/>
-    </row>
-    <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="96"/>
-      <c r="B63" s="97"/>
-      <c r="C63" s="100" t="s">
-        <v>28</v>
-      </c>
-      <c r="D63" s="97"/>
-      <c r="E63" s="100" t="s">
-        <v>11</v>
-      </c>
-      <c r="F63" s="101"/>
-      <c r="G63" s="101"/>
-      <c r="H63" s="101"/>
-      <c r="I63" s="101"/>
-      <c r="J63" s="101"/>
-      <c r="K63" s="97"/>
-      <c r="L63" s="102" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="98"/>
-      <c r="B64" s="99"/>
-      <c r="C64" s="104" t="s">
-        <v>30</v>
-      </c>
-      <c r="D64" s="105"/>
-      <c r="E64" s="104" t="s">
-        <v>31</v>
-      </c>
-      <c r="F64" s="105"/>
-      <c r="G64" s="105"/>
-      <c r="H64" s="105"/>
-      <c r="I64" s="105"/>
-      <c r="J64" s="105"/>
-      <c r="K64" s="105"/>
-      <c r="L64" s="103"/>
+      <c r="F64" s="168"/>
+      <c r="G64" s="168"/>
+      <c r="H64" s="168"/>
+      <c r="I64" s="168"/>
+      <c r="J64" s="168"/>
+      <c r="K64" s="168"/>
+      <c r="L64" s="130"/>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="71" t="s">
+      <c r="A65" s="177" t="s">
         <v>46</v>
       </c>
-      <c r="B65" s="72"/>
-      <c r="C65" s="73"/>
-      <c r="D65" s="74"/>
-      <c r="E65" s="76"/>
-      <c r="F65" s="77"/>
-      <c r="G65" s="77"/>
-      <c r="H65" s="77"/>
-      <c r="I65" s="77"/>
-      <c r="J65" s="77"/>
-      <c r="K65" s="78"/>
-      <c r="L65" s="82"/>
+      <c r="B65" s="178"/>
+      <c r="C65" s="179"/>
+      <c r="D65" s="180"/>
+      <c r="E65" s="141"/>
+      <c r="F65" s="142"/>
+      <c r="G65" s="142"/>
+      <c r="H65" s="142"/>
+      <c r="I65" s="142"/>
+      <c r="J65" s="142"/>
+      <c r="K65" s="143"/>
+      <c r="L65" s="181"/>
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="71"/>
-      <c r="B66" s="72"/>
+      <c r="A66" s="177"/>
+      <c r="B66" s="178"/>
       <c r="C66" s="75"/>
       <c r="D66" s="75"/>
-      <c r="E66" s="79"/>
-      <c r="F66" s="80"/>
-      <c r="G66" s="80"/>
-      <c r="H66" s="80"/>
-      <c r="I66" s="80"/>
-      <c r="J66" s="80"/>
-      <c r="K66" s="81"/>
-      <c r="L66" s="83"/>
+      <c r="E66" s="144"/>
+      <c r="F66" s="145"/>
+      <c r="G66" s="145"/>
+      <c r="H66" s="145"/>
+      <c r="I66" s="145"/>
+      <c r="J66" s="145"/>
+      <c r="K66" s="146"/>
+      <c r="L66" s="67"/>
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="71" t="s">
+      <c r="A67" s="177" t="s">
         <v>47</v>
       </c>
-      <c r="B67" s="72"/>
-      <c r="C67" s="86"/>
-      <c r="D67" s="87"/>
-      <c r="E67" s="86"/>
-      <c r="F67" s="90"/>
-      <c r="G67" s="90"/>
-      <c r="H67" s="90"/>
-      <c r="I67" s="90"/>
-      <c r="J67" s="90"/>
-      <c r="K67" s="87"/>
-      <c r="L67" s="83"/>
+      <c r="B67" s="178"/>
+      <c r="C67" s="184"/>
+      <c r="D67" s="185"/>
+      <c r="E67" s="184"/>
+      <c r="F67" s="188"/>
+      <c r="G67" s="188"/>
+      <c r="H67" s="188"/>
+      <c r="I67" s="188"/>
+      <c r="J67" s="188"/>
+      <c r="K67" s="185"/>
+      <c r="L67" s="67"/>
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="84"/>
-      <c r="B68" s="85"/>
-      <c r="C68" s="88"/>
-      <c r="D68" s="89"/>
-      <c r="E68" s="88"/>
-      <c r="F68" s="91"/>
-      <c r="G68" s="91"/>
-      <c r="H68" s="91"/>
-      <c r="I68" s="91"/>
-      <c r="J68" s="91"/>
-      <c r="K68" s="89"/>
-      <c r="L68" s="92"/>
+      <c r="A68" s="182"/>
+      <c r="B68" s="183"/>
+      <c r="C68" s="186"/>
+      <c r="D68" s="187"/>
+      <c r="E68" s="186"/>
+      <c r="F68" s="189"/>
+      <c r="G68" s="189"/>
+      <c r="H68" s="189"/>
+      <c r="I68" s="189"/>
+      <c r="J68" s="189"/>
+      <c r="K68" s="187"/>
+      <c r="L68" s="190"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A69" s="66"/>
-      <c r="B69" s="66"/>
-      <c r="C69" s="66"/>
-      <c r="D69" s="66"/>
-      <c r="E69" s="66"/>
-      <c r="F69" s="66"/>
-      <c r="G69" s="66"/>
-      <c r="H69" s="66"/>
-      <c r="I69" s="66"/>
-      <c r="J69" s="66"/>
-      <c r="K69" s="66"/>
-      <c r="L69" s="66"/>
+      <c r="A69" s="175"/>
+      <c r="B69" s="175"/>
+      <c r="C69" s="175"/>
+      <c r="D69" s="175"/>
+      <c r="E69" s="175"/>
+      <c r="F69" s="175"/>
+      <c r="G69" s="175"/>
+      <c r="H69" s="175"/>
+      <c r="I69" s="175"/>
+      <c r="J69" s="175"/>
+      <c r="K69" s="175"/>
+      <c r="L69" s="175"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" selectLockedCells="1" sort="0"/>
   <mergeCells count="154">
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:E12"/>
-    <mergeCell ref="F11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="C1:H2"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:K8"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:K19"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="D13:E14"/>
-    <mergeCell ref="F13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:E16"/>
-    <mergeCell ref="F15:K16"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="B43:I44"/>
-    <mergeCell ref="J43:L44"/>
-    <mergeCell ref="A45:L45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="D46:K46"/>
-    <mergeCell ref="L46:L47"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="D47:K47"/>
-    <mergeCell ref="A48:C49"/>
-    <mergeCell ref="D48:K49"/>
-    <mergeCell ref="L48:L49"/>
-    <mergeCell ref="A50:L50"/>
-    <mergeCell ref="A51:L51"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="E52:E60"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="K52:L52"/>
-    <mergeCell ref="A53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="K53:L53"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="K54:L54"/>
-    <mergeCell ref="A55:C56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="K55:L55"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="E64:K64"/>
-    <mergeCell ref="A59:C60"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="K59:L59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="K56:L56"/>
-    <mergeCell ref="A57:C58"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="K57:L57"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
     <mergeCell ref="A69:L69"/>
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="D21:E21"/>
@@ -4254,30 +4177,125 @@
     <mergeCell ref="C63:D63"/>
     <mergeCell ref="E63:K63"/>
     <mergeCell ref="L63:L64"/>
-    <mergeCell ref="A1:B2"/>
     <mergeCell ref="J31:K31"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:K64"/>
+    <mergeCell ref="A59:C60"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="K59:L59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="A57:C58"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="A48:C49"/>
+    <mergeCell ref="D48:K49"/>
+    <mergeCell ref="L48:L49"/>
+    <mergeCell ref="A50:L50"/>
+    <mergeCell ref="A51:L51"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="E52:E60"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="A53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="A55:C56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="B43:I44"/>
+    <mergeCell ref="J43:L44"/>
+    <mergeCell ref="A45:L45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="D46:K46"/>
+    <mergeCell ref="L46:L47"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D47:K47"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J40:K40"/>
     <mergeCell ref="J32:K32"/>
     <mergeCell ref="J33:K33"/>
     <mergeCell ref="J34:K34"/>
     <mergeCell ref="J35:K35"/>
     <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:K19"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D13:E14"/>
+    <mergeCell ref="F13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:E16"/>
+    <mergeCell ref="F15:K16"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="D17:E18"/>
     <mergeCell ref="F17:K18"/>
+    <mergeCell ref="C1:H2"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:L4"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:E12"/>
+    <mergeCell ref="F11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:K8"/>
     <mergeCell ref="D9:E10"/>
     <mergeCell ref="F9:K10"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Please enter an 'X' if item is taxable, or leave BLANK if non-taxable." sqref="I21:I41" xr:uid="{B7093725-9997-4EBC-B647-A19967A14D48}">
